--- a/examples/SRA_metadata_example.xlsx
+++ b/examples/SRA_metadata_example.xlsx
@@ -1233,7 +1233,7 @@
     <t>A04_S4</t>
   </si>
   <si>
-    <t>CBER virus panel  + HEV</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>A01_S1_R1_001.fastq.gz</t>
